--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\PRUEBAS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BFB0E5-A2EB-4D2E-B9E4-85299540E365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857CEBAC-8FDA-476D-ADF3-42B9A48B934C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7005" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7734" uniqueCount="643">
   <si>
     <t>Fecha</t>
   </si>
@@ -1603,6 +1603,126 @@
     <t>2026-12-14</t>
   </si>
   <si>
+    <t>AGROFORESTAL</t>
+  </si>
+  <si>
+    <t>SOL 10199</t>
+  </si>
+  <si>
+    <t>CONFERENCIA AGROFORESTAL</t>
+  </si>
+  <si>
+    <t>AUDITORIO PAB. O</t>
+  </si>
+  <si>
+    <t>PODIO / 2 MESAS CON MANTEL / 2 SILLAS</t>
+  </si>
+  <si>
+    <t>MARKETING</t>
+  </si>
+  <si>
+    <t>VISITA COLEGIO NEWTON</t>
+  </si>
+  <si>
+    <t>SEPARAR 1 MESA / LIMPIEZA GENERAL</t>
+  </si>
+  <si>
+    <t>Visitas externas</t>
+  </si>
+  <si>
+    <t>OT 84237</t>
+  </si>
+  <si>
+    <t>JUEGO RESILIENCIA CLIMÁTICA</t>
+  </si>
+  <si>
+    <t>06 MESAS / 30 SILLAS / 01 MESA CON MANTEL / 01 MESA EN ESTRADO / 04 SILLAS EN ESTRADO</t>
+  </si>
+  <si>
+    <t>SOL 10265</t>
+  </si>
+  <si>
+    <t>CONFERENCIA VETERINARIA</t>
+  </si>
+  <si>
+    <t>02 MESAS CON MANTEL / 02 SILLAS</t>
+  </si>
+  <si>
+    <t>SIMULACIÓN</t>
+  </si>
+  <si>
+    <t>SOL 10323</t>
+  </si>
+  <si>
+    <t>EVENTO SIMULACIÓN</t>
+  </si>
+  <si>
+    <t>AUDITORIO PAB. L - 204</t>
+  </si>
+  <si>
+    <t>03 MESAS CON MANTEL</t>
+  </si>
+  <si>
+    <t>SOL 10322</t>
+  </si>
+  <si>
+    <t>DERECHO</t>
+  </si>
+  <si>
+    <t>SOL 10353</t>
+  </si>
+  <si>
+    <t>CHARLA MINJUS</t>
+  </si>
+  <si>
+    <t>AUDITORIO PABELLÓN O</t>
+  </si>
+  <si>
+    <t>02 MESAS CON MANTEL / 02 SILLAS / 01 PODIO / 01 BANNER / 01 BANDERA</t>
+  </si>
+  <si>
+    <t>ING. AMBIENTAL</t>
+  </si>
+  <si>
+    <t>SOL 10357</t>
+  </si>
+  <si>
+    <t>VISITA A PTAR</t>
+  </si>
+  <si>
+    <t>PTAR</t>
+  </si>
+  <si>
+    <t>LIMPIEZA DE PTAR</t>
+  </si>
+  <si>
+    <t>2026-10-04</t>
+  </si>
+  <si>
+    <t>ESTOMATOLOGÍA</t>
+  </si>
+  <si>
+    <t>SOL 10134</t>
+  </si>
+  <si>
+    <t>EVENTO ESTOMATOLOGÍA</t>
+  </si>
+  <si>
+    <t>27 SILLAS / 05 MESAS CON MANTEL</t>
+  </si>
+  <si>
+    <t>SOL 10234</t>
+  </si>
+  <si>
+    <t>TORNEO CACHIMBOS 2026-2</t>
+  </si>
+  <si>
+    <t>VILLA 2</t>
+  </si>
+  <si>
+    <t>06 PIES DE CAMPO ALREDEDOR DE CANCHAS DE VÓLEY, BÁSQUET Y FULBITO / BACKING EN CANCHAS DE FULBITO + 4 CUBOS CIENTÍFICA / 01 PUNTO DE LUZ CERCA DE CANCHAS DE FULBITO / 02 TOLDOS FUERA DE LOS CAMPOS / PLUMAS EN INGRESO VILLA 2 / 04 MESAS CON 3 SILLAS CADA UNA (1 VÓLEY, 1 BÁSQUET, 2 FULBITO) / 01 MESA LARGA CON MANTEL AZUL PARA PREMIACIÓN / MONTAJE 08:00 - DESMONTAJE 18:00</t>
+  </si>
+  <si>
     <t>Académico</t>
   </si>
   <si>
@@ -1732,126 +1852,6 @@
     <t>Ordenadas por fecha y hora</t>
   </si>
   <si>
-    <t>AGROFORESTAL</t>
-  </si>
-  <si>
-    <t>SOL 10199</t>
-  </si>
-  <si>
-    <t>CONFERENCIA AGROFORESTAL</t>
-  </si>
-  <si>
-    <t>AUDITORIO PAB. O</t>
-  </si>
-  <si>
-    <t>PODIO / 2 MESAS CON MANTEL / 2 SILLAS</t>
-  </si>
-  <si>
-    <t>MARKETING</t>
-  </si>
-  <si>
-    <t>VISITA COLEGIO NEWTON</t>
-  </si>
-  <si>
-    <t>SEPARAR 1 MESA / LIMPIEZA GENERAL</t>
-  </si>
-  <si>
-    <t>Visitas externas</t>
-  </si>
-  <si>
-    <t>OT 84237</t>
-  </si>
-  <si>
-    <t>JUEGO RESILIENCIA CLIMÁTICA</t>
-  </si>
-  <si>
-    <t>06 MESAS / 30 SILLAS / 01 MESA CON MANTEL / 01 MESA EN ESTRADO / 04 SILLAS EN ESTRADO</t>
-  </si>
-  <si>
-    <t>SOL 10265</t>
-  </si>
-  <si>
-    <t>CONFERENCIA VETERINARIA</t>
-  </si>
-  <si>
-    <t>02 MESAS CON MANTEL / 02 SILLAS</t>
-  </si>
-  <si>
-    <t>SIMULACIÓN</t>
-  </si>
-  <si>
-    <t>SOL 10323</t>
-  </si>
-  <si>
-    <t>EVENTO SIMULACIÓN</t>
-  </si>
-  <si>
-    <t>AUDITORIO PAB. L - 204</t>
-  </si>
-  <si>
-    <t>03 MESAS CON MANTEL</t>
-  </si>
-  <si>
-    <t>SOL 10322</t>
-  </si>
-  <si>
-    <t>DERECHO</t>
-  </si>
-  <si>
-    <t>SOL 10353</t>
-  </si>
-  <si>
-    <t>CHARLA MINJUS</t>
-  </si>
-  <si>
-    <t>AUDITORIO PABELLÓN O</t>
-  </si>
-  <si>
-    <t>02 MESAS CON MANTEL / 02 SILLAS / 01 PODIO / 01 BANNER / 01 BANDERA</t>
-  </si>
-  <si>
-    <t>ING. AMBIENTAL</t>
-  </si>
-  <si>
-    <t>SOL 10357</t>
-  </si>
-  <si>
-    <t>VISITA A PTAR</t>
-  </si>
-  <si>
-    <t>PTAR</t>
-  </si>
-  <si>
-    <t>LIMPIEZA DE PTAR</t>
-  </si>
-  <si>
-    <t>2026-10-04</t>
-  </si>
-  <si>
-    <t>ESTOMATOLOGÍA</t>
-  </si>
-  <si>
-    <t>SOL 10134</t>
-  </si>
-  <si>
-    <t>EVENTO ESTOMATOLOGÍA</t>
-  </si>
-  <si>
-    <t>27 SILLAS / 05 MESAS CON MANTEL</t>
-  </si>
-  <si>
-    <t>SOL 10234</t>
-  </si>
-  <si>
-    <t>TORNEO CACHIMBOS 2026-2</t>
-  </si>
-  <si>
-    <t>VILLA 2</t>
-  </si>
-  <si>
-    <t>06 PIES DE CAMPO ALREDEDOR DE CANCHAS DE VÓLEY, BÁSQUET Y FULBITO / BACKING EN CANCHAS DE FULBITO + 4 CUBOS CIENTÍFICA / 01 PUNTO DE LUZ CERCA DE CANCHAS DE FULBITO / 02 TOLDOS FUERA DE LOS CAMPOS / PLUMAS EN INGRESO VILLA 2 / 04 MESAS CON 3 SILLAS CADA UNA (1 VÓLEY, 1 BÁSQUET, 2 FULBITO) / 01 MESA LARGA CON MANTEL AZUL PARA PREMIACIÓN / MONTAJE 08:00 - DESMONTAJE 18:00</t>
-  </si>
-  <si>
     <t>Actualización GitHub 03/09/2026</t>
   </si>
   <si>
@@ -1862,6 +1862,156 @@
   </si>
   <si>
     <t>Listo para dashboard</t>
+  </si>
+  <si>
+    <t>SOL 10398</t>
+  </si>
+  <si>
+    <t>EXPLORA CIENTIFICA</t>
+  </si>
+  <si>
+    <t>PABELLON I</t>
+  </si>
+  <si>
+    <t>ZONA DE REGISTRO (ENTRADA PABELLON I): 01 TOLDO / 01 MESA CON MANTEL / 03 SILLAS / 03 TOMACORRIENTES; ZONA DE VENTAS (SALA DE ESTUDIO PISO 3 PAB. O): 20 SILLAS / 01 MESA CON MANTEL / 03 SILLAS / 01 TOMACORRIENTE; ZONA DE SNACKS (COSTADO DE VENTAS): 01 MESA CON MANTEL</t>
+  </si>
+  <si>
+    <t>VK SETIEMBRE</t>
+  </si>
+  <si>
+    <t>Expresión Corporal</t>
+  </si>
+  <si>
+    <t>Aula K-104</t>
+  </si>
+  <si>
+    <t>Espacio limpio/mobiliario retirado / Horario: 11:00-13:00</t>
+  </si>
+  <si>
+    <t>Aula K-213</t>
+  </si>
+  <si>
+    <t>Espacio limpio/mobiliario retirado / Horario: 13:00-15:00</t>
+  </si>
+  <si>
+    <t>Salsa</t>
+  </si>
+  <si>
+    <t>Espacio limpio / punto de luz / Horario: 13:00-15:00</t>
+  </si>
+  <si>
+    <t>Espacio limpio / punto de luz / Horario: 15:00-17:00</t>
+  </si>
+  <si>
+    <t>Comunicación Teatral Efectiva</t>
+  </si>
+  <si>
+    <t>Aula K-107</t>
+  </si>
+  <si>
+    <t>Espacio limpio/mobiliario retirado / Horario: 10:00-12:00</t>
+  </si>
+  <si>
+    <t>Impro para Todos</t>
+  </si>
+  <si>
+    <t>Espacio limpio/mobiliario retirado / Horario: 12:00-14:00</t>
+  </si>
+  <si>
+    <t>Club de Literatura</t>
+  </si>
+  <si>
+    <t>Aula K-205</t>
+  </si>
+  <si>
+    <t>Espacio limpio / Horario: 15:00-17:00</t>
+  </si>
+  <si>
+    <t>Terapia de las Artes para el Bienestar y Manejo del Estrés</t>
+  </si>
+  <si>
+    <t>Aula J-103</t>
+  </si>
+  <si>
+    <t>Espacio limpio/mobiliario retirado / Horario: 15:00-17:00</t>
+  </si>
+  <si>
+    <t>Aula K-106</t>
+  </si>
+  <si>
+    <t>Espacio limpio / Horario: 17:00-18:40</t>
+  </si>
+  <si>
+    <t>Espacio limpio / Horario: 18:30-20:30</t>
+  </si>
+  <si>
+    <t>Dibujo de Manga</t>
+  </si>
+  <si>
+    <t>Aula K-212</t>
+  </si>
+  <si>
+    <t>Espacio limpio / Horario: 11:00-13:00</t>
+  </si>
+  <si>
+    <t>Espacio limpio / punto de luz / Horario: 18:30-20:30</t>
+  </si>
+  <si>
+    <t>Fotografía para Todos</t>
+  </si>
+  <si>
+    <t>Aula J-104</t>
+  </si>
+  <si>
+    <t>Clown</t>
+  </si>
+  <si>
+    <t>Aula K-211</t>
+  </si>
+  <si>
+    <t>Aula académica 3 / I-202</t>
+  </si>
+  <si>
+    <t>Espacio limpio / Horario: 13:00-15:00</t>
+  </si>
+  <si>
+    <t>Aula K-103</t>
+  </si>
+  <si>
+    <t>Aula N-203</t>
+  </si>
+  <si>
+    <t>Espacio limpio / Horario: 17:00-19:00</t>
+  </si>
+  <si>
+    <t>Dibujo y Pintura</t>
+  </si>
+  <si>
+    <t>Espacio limpio/mobiliario retirado / Horario: 14:00-16:00</t>
+  </si>
+  <si>
+    <t>Espacio limpio / Horario: 14:00-16:00</t>
+  </si>
+  <si>
+    <t>Herramientas Teatrales</t>
+  </si>
+  <si>
+    <t>Aula K-203</t>
+  </si>
+  <si>
+    <t>Clown (Horario 2)</t>
+  </si>
+  <si>
+    <t>Espacio limpio/mobiliario retirado / Horario: 16:00-18:00</t>
+  </si>
+  <si>
+    <t>Edición de Vídeo</t>
+  </si>
+  <si>
+    <t>Folklore Peruano para Todos</t>
+  </si>
+  <si>
+    <t>Espacio limpio / punto de luz / Horario: 11:00-13:00</t>
   </si>
 </sst>
 </file>
@@ -1988,7 +2138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2063,6 +2213,10 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2309,18 +2463,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L700"/>
+  <dimension ref="A1:L773"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="21" style="9" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="12" style="10" customWidth="1"/>
-    <col min="5" max="5" width="38.75" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="45" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="10" width="15" customWidth="1"/>
+    <col min="1" max="1" width="12" style="9" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="16" style="10" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="42" customWidth="1"/>
+    <col min="8" max="10" width="15" customWidth="1"/>
     <col min="11" max="11" width="5.75" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
   </cols>
@@ -2831,7 +2984,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15">
+    <row r="17" spans="1:10" ht="28.5">
       <c r="A17" s="22" t="s">
         <v>45</v>
       </c>
@@ -2863,7 +3016,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15">
+    <row r="18" spans="1:10" ht="28.5">
       <c r="A18" s="22" t="s">
         <v>89</v>
       </c>
@@ -2895,7 +3048,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15">
+    <row r="19" spans="1:10" ht="28.5">
       <c r="A19" s="22" t="s">
         <v>90</v>
       </c>
@@ -2927,7 +3080,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15">
+    <row r="20" spans="1:10" ht="28.5">
       <c r="A20" s="22" t="s">
         <v>72</v>
       </c>
@@ -5295,7 +5448,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="15">
+    <row r="94" spans="1:10" ht="28.5">
       <c r="A94" s="22" t="s">
         <v>51</v>
       </c>
@@ -5487,7 +5640,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="15">
+    <row r="100" spans="1:10" ht="28.5">
       <c r="A100" s="22" t="s">
         <v>120</v>
       </c>
@@ -7913,7 +8066,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="176" spans="1:10" ht="42.75">
+    <row r="176" spans="1:10" ht="57">
       <c r="A176" s="22" t="s">
         <v>230</v>
       </c>
@@ -7945,7 +8098,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="42.75">
+    <row r="177" spans="1:10" ht="57">
       <c r="A177" s="22" t="s">
         <v>234</v>
       </c>
@@ -8137,7 +8290,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="15">
+    <row r="183" spans="1:10" ht="28.5">
       <c r="A183" s="22" t="s">
         <v>126</v>
       </c>
@@ -8297,7 +8450,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="28.5">
+    <row r="188" spans="1:10" ht="42.75">
       <c r="A188" s="22" t="s">
         <v>126</v>
       </c>
@@ -8361,7 +8514,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="156.75">
+    <row r="190" spans="1:10" ht="171">
       <c r="A190" s="22" t="s">
         <v>126</v>
       </c>
@@ -8393,7 +8546,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="213.75">
+    <row r="191" spans="1:10" ht="228">
       <c r="A191" s="22" t="s">
         <v>199</v>
       </c>
@@ -8681,7 +8834,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="200" spans="1:10" ht="15">
+    <row r="200" spans="1:10" ht="28.5">
       <c r="A200" s="22" t="s">
         <v>296</v>
       </c>
@@ -8809,7 +8962,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="204" spans="1:10" ht="15">
+    <row r="204" spans="1:10" ht="28.5">
       <c r="A204" s="22" t="s">
         <v>97</v>
       </c>
@@ -8841,7 +8994,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="205" spans="1:10" ht="15">
+    <row r="205" spans="1:10" ht="28.5">
       <c r="A205" s="22" t="s">
         <v>283</v>
       </c>
@@ -9353,7 +9506,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="221" spans="1:10" ht="42.75">
+    <row r="221" spans="1:10" ht="57">
       <c r="A221" s="22" t="s">
         <v>306</v>
       </c>
@@ -9449,7 +9602,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="224" spans="1:10" ht="42.75">
+    <row r="224" spans="1:10" ht="57">
       <c r="A224" s="22" t="s">
         <v>306</v>
       </c>
@@ -11163,7 +11316,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="279" spans="1:10" ht="42.75">
+    <row r="279" spans="1:10" ht="57">
       <c r="A279" s="22"/>
       <c r="B279" s="14" t="s">
         <v>11</v>
@@ -11255,7 +11408,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="282" spans="1:10" ht="42.75">
+    <row r="282" spans="1:10" ht="57">
       <c r="A282" s="22"/>
       <c r="B282" s="14" t="s">
         <v>73</v>
@@ -11345,7 +11498,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="285" spans="1:10" ht="15">
+    <row r="285" spans="1:10" ht="28.5">
       <c r="A285" s="22">
         <v>46214</v>
       </c>
@@ -24285,7 +24438,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="690" spans="1:10">
+    <row r="690" spans="1:10" ht="28.5">
       <c r="A690" s="23" t="s">
         <v>395</v>
       </c>
@@ -24293,19 +24446,19 @@
         <v>31</v>
       </c>
       <c r="C690" s="1" t="s">
-        <v>549</v>
+        <v>506</v>
       </c>
       <c r="D690" s="1" t="s">
-        <v>550</v>
+        <v>507</v>
       </c>
       <c r="E690" s="1" t="s">
-        <v>551</v>
+        <v>508</v>
       </c>
       <c r="F690" s="1" t="s">
-        <v>552</v>
+        <v>509</v>
       </c>
       <c r="G690" s="1" t="s">
-        <v>553</v>
+        <v>510</v>
       </c>
       <c r="H690" s="1" t="s">
         <v>17</v>
@@ -24325,31 +24478,31 @@
         <v>11</v>
       </c>
       <c r="C691" s="1" t="s">
-        <v>554</v>
+        <v>511</v>
       </c>
       <c r="D691" s="8" t="s">
         <v>28</v>
       </c>
       <c r="E691" s="1" t="s">
-        <v>555</v>
+        <v>512</v>
       </c>
       <c r="F691" s="1" t="s">
         <v>294</v>
       </c>
       <c r="G691" s="1" t="s">
-        <v>556</v>
+        <v>513</v>
       </c>
       <c r="H691" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I691" s="1" t="s">
-        <v>557</v>
+        <v>514</v>
       </c>
       <c r="J691" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="692" spans="1:10" s="9" customFormat="1" ht="28.5">
+    <row r="692" spans="1:10" s="9" customFormat="1" ht="42.75">
       <c r="A692" s="26" t="s">
         <v>422</v>
       </c>
@@ -24357,19 +24510,19 @@
         <v>11</v>
       </c>
       <c r="C692" s="13" t="s">
-        <v>549</v>
+        <v>506</v>
       </c>
       <c r="D692" s="13" t="s">
-        <v>558</v>
+        <v>515</v>
       </c>
       <c r="E692" s="13" t="s">
-        <v>559</v>
+        <v>516</v>
       </c>
       <c r="F692" s="13" t="s">
-        <v>552</v>
+        <v>509</v>
       </c>
       <c r="G692" s="13" t="s">
-        <v>560</v>
+        <v>517</v>
       </c>
       <c r="H692" s="13" t="s">
         <v>17</v>
@@ -24381,7 +24534,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="693" spans="1:10" s="9" customFormat="1" ht="28.5">
+    <row r="693" spans="1:10" s="9" customFormat="1" ht="42.75">
       <c r="A693" s="26" t="s">
         <v>423</v>
       </c>
@@ -24389,19 +24542,19 @@
         <v>11</v>
       </c>
       <c r="C693" s="13" t="s">
-        <v>549</v>
+        <v>506</v>
       </c>
       <c r="D693" s="13" t="s">
-        <v>558</v>
+        <v>515</v>
       </c>
       <c r="E693" s="13" t="s">
-        <v>559</v>
+        <v>516</v>
       </c>
       <c r="F693" s="13" t="s">
-        <v>552</v>
+        <v>509</v>
       </c>
       <c r="G693" s="13" t="s">
-        <v>560</v>
+        <v>517</v>
       </c>
       <c r="H693" s="13" t="s">
         <v>17</v>
@@ -24424,16 +24577,16 @@
         <v>332</v>
       </c>
       <c r="D694" s="8" t="s">
-        <v>561</v>
+        <v>518</v>
       </c>
       <c r="E694" s="1" t="s">
-        <v>562</v>
+        <v>519</v>
       </c>
       <c r="F694" s="1" t="s">
-        <v>552</v>
+        <v>509</v>
       </c>
       <c r="G694" s="1" t="s">
-        <v>563</v>
+        <v>520</v>
       </c>
       <c r="H694" s="1" t="s">
         <v>17</v>
@@ -24453,19 +24606,19 @@
         <v>11</v>
       </c>
       <c r="C695" s="1" t="s">
-        <v>564</v>
+        <v>521</v>
       </c>
       <c r="D695" s="8" t="s">
-        <v>565</v>
+        <v>522</v>
       </c>
       <c r="E695" s="1" t="s">
-        <v>566</v>
+        <v>523</v>
       </c>
       <c r="F695" s="1" t="s">
-        <v>567</v>
+        <v>524</v>
       </c>
       <c r="G695" s="1" t="s">
-        <v>568</v>
+        <v>525</v>
       </c>
       <c r="H695" s="1" t="s">
         <v>17</v>
@@ -24485,19 +24638,19 @@
         <v>11</v>
       </c>
       <c r="C696" s="1" t="s">
-        <v>564</v>
+        <v>521</v>
       </c>
       <c r="D696" s="8" t="s">
-        <v>569</v>
+        <v>526</v>
       </c>
       <c r="E696" s="1" t="s">
-        <v>566</v>
+        <v>523</v>
       </c>
       <c r="F696" s="1" t="s">
-        <v>567</v>
+        <v>524</v>
       </c>
       <c r="G696" s="1" t="s">
-        <v>568</v>
+        <v>525</v>
       </c>
       <c r="H696" s="1" t="s">
         <v>17</v>
@@ -24517,19 +24670,19 @@
         <v>119</v>
       </c>
       <c r="C697" s="1" t="s">
-        <v>570</v>
+        <v>527</v>
       </c>
       <c r="D697" s="8" t="s">
-        <v>571</v>
+        <v>528</v>
       </c>
       <c r="E697" s="1" t="s">
-        <v>572</v>
+        <v>529</v>
       </c>
       <c r="F697" s="1" t="s">
-        <v>573</v>
+        <v>530</v>
       </c>
       <c r="G697" s="1" t="s">
-        <v>574</v>
+        <v>531</v>
       </c>
       <c r="H697" s="1" t="s">
         <v>17</v>
@@ -24549,19 +24702,19 @@
         <v>31</v>
       </c>
       <c r="C698" s="1" t="s">
-        <v>575</v>
+        <v>532</v>
       </c>
       <c r="D698" s="8" t="s">
-        <v>576</v>
+        <v>533</v>
       </c>
       <c r="E698" s="1" t="s">
-        <v>577</v>
+        <v>534</v>
       </c>
       <c r="F698" s="1" t="s">
-        <v>578</v>
+        <v>535</v>
       </c>
       <c r="G698" s="1" t="s">
-        <v>579</v>
+        <v>536</v>
       </c>
       <c r="H698" s="1" t="s">
         <v>17</v>
@@ -24575,25 +24728,25 @@
     </row>
     <row r="699" spans="1:10">
       <c r="A699" s="26" t="s">
-        <v>580</v>
+        <v>537</v>
       </c>
       <c r="B699" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C699" s="1" t="s">
-        <v>581</v>
+        <v>538</v>
       </c>
       <c r="D699" s="8" t="s">
-        <v>582</v>
+        <v>539</v>
       </c>
       <c r="E699" s="1" t="s">
-        <v>583</v>
+        <v>540</v>
       </c>
       <c r="F699" s="1" t="s">
-        <v>552</v>
+        <v>509</v>
       </c>
       <c r="G699" s="1" t="s">
-        <v>584</v>
+        <v>541</v>
       </c>
       <c r="H699" s="1" t="s">
         <v>17</v>
@@ -24605,7 +24758,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="700" spans="1:10" ht="142.5">
+    <row r="700" spans="1:10" ht="156.75">
       <c r="A700" s="26" t="s">
         <v>422</v>
       </c>
@@ -24616,16 +24769,16 @@
         <v>21</v>
       </c>
       <c r="D700" s="8" t="s">
-        <v>585</v>
+        <v>542</v>
       </c>
       <c r="E700" s="1" t="s">
-        <v>586</v>
+        <v>543</v>
       </c>
       <c r="F700" s="1" t="s">
-        <v>587</v>
+        <v>544</v>
       </c>
       <c r="G700" s="1" t="s">
-        <v>588</v>
+        <v>545</v>
       </c>
       <c r="H700" s="1" t="s">
         <v>17</v>
@@ -24634,6 +24787,2342 @@
         <v>18</v>
       </c>
       <c r="J700" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="701" spans="1:10" ht="114">
+      <c r="A701" s="28" t="s">
+        <v>433</v>
+      </c>
+      <c r="B701" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C701" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D701" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="E701" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="F701" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="G701" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="H701" t="s">
+        <v>17</v>
+      </c>
+      <c r="I701" t="s">
+        <v>18</v>
+      </c>
+      <c r="J701" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="702" spans="1:10" ht="114">
+      <c r="A702" s="28">
+        <v>46284</v>
+      </c>
+      <c r="B702" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C702" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D702" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="E702" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="F702" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="G702" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="H702" t="s">
+        <v>17</v>
+      </c>
+      <c r="I702" t="s">
+        <v>18</v>
+      </c>
+      <c r="J702" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="703" spans="1:10" ht="28.5">
+      <c r="A703" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="B703" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C703" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D703" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E703" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="F703" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="G703" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="H703" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I703" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J703" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="704" spans="1:10" ht="28.5">
+      <c r="A704" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="B704" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C704" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D704" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E704" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="F704" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="G704" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="H704" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I704" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J704" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="705" spans="1:10" ht="28.5">
+      <c r="A705" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="B705" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C705" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D705" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E705" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="F705" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G705" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="H705" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I705" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J705" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="706" spans="1:10" ht="28.5">
+      <c r="A706" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="B706" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C706" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D706" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E706" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="F706" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G706" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="H706" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I706" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J706" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="707" spans="1:10" ht="28.5">
+      <c r="A707" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="B707" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C707" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D707" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E707" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="F707" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="G707" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="H707" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I707" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J707" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="708" spans="1:10" ht="28.5">
+      <c r="A708" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="B708" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C708" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D708" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E708" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="F708" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="G708" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="H708" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I708" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J708" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="709" spans="1:10">
+      <c r="A709" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="B709" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C709" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D709" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E709" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="F709" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="G709" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="H709" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I709" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J709" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="710" spans="1:10" ht="28.5">
+      <c r="A710" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="B710" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C710" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D710" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E710" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="F710" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="G710" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="H710" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I710" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J710" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="711" spans="1:10">
+      <c r="A711" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="B711" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C711" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D711" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E711" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F711" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="G711" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="H711" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I711" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J711" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="712" spans="1:10">
+      <c r="A712" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="B712" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C712" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D712" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E712" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F712" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="G712" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="H712" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I712" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J712" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="713" spans="1:10">
+      <c r="A713" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="B713" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C713" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D713" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E713" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="F713" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="G713" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="H713" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I713" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J713" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="714" spans="1:10" ht="28.5">
+      <c r="A714" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="B714" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C714" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D714" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E714" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="F714" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="G714" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="H714" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I714" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J714" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="715" spans="1:10" ht="28.5">
+      <c r="A715" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="B715" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C715" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D715" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E715" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F715" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G715" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="H715" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I715" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J715" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="716" spans="1:10">
+      <c r="A716" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="B716" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C716" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D716" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E716" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="F716" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="G716" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="H716" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I716" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J716" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="717" spans="1:10" ht="28.5">
+      <c r="A717" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="B717" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C717" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D717" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E717" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="F717" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="G717" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="H717" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I717" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J717" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="718" spans="1:10">
+      <c r="A718" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="B718" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C718" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D718" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E718" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="F718" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="G718" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="H718" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I718" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J718" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="719" spans="1:10">
+      <c r="A719" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="B719" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C719" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D719" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E719" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="F719" s="6" t="s">
+        <v>630</v>
+      </c>
+      <c r="G719" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="H719" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I719" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J719" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="720" spans="1:10">
+      <c r="A720" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="B720" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C720" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D720" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E720" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="F720" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="G720" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="H720" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I720" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J720" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="721" spans="1:10">
+      <c r="A721" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="B721" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C721" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D721" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E721" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F721" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="G721" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="H721" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I721" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J721" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="722" spans="1:10">
+      <c r="A722" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="B722" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C722" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D722" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E722" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="F722" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="G722" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="H722" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I722" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J722" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="723" spans="1:10" ht="28.5">
+      <c r="A723" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="B723" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C723" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D723" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E723" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="F723" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="G723" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="H723" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I723" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J723" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="724" spans="1:10" ht="28.5">
+      <c r="A724" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="B724" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C724" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D724" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E724" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="F724" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="G724" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="H724" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I724" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J724" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="725" spans="1:10">
+      <c r="A725" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="B725" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C725" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D725" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E725" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="F725" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="G725" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="H725" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I725" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J725" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="726" spans="1:10" ht="28.5">
+      <c r="A726" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="B726" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C726" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D726" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E726" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="F726" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="G726" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="H726" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I726" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J726" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="727" spans="1:10">
+      <c r="A727" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="B727" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C727" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D727" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E727" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="F727" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="G727" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="H727" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I727" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J727" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="728" spans="1:10" ht="28.5">
+      <c r="A728" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="B728" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C728" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D728" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E728" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="F728" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="G728" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="H728" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I728" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J728" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="729" spans="1:10">
+      <c r="A729" s="13" t="s">
+        <v>434</v>
+      </c>
+      <c r="B729" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C729" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D729" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E729" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="F729" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="G729" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="H729" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I729" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J729" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="730" spans="1:10" ht="28.5">
+      <c r="A730" s="13" t="s">
+        <v>434</v>
+      </c>
+      <c r="B730" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C730" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D730" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E730" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F730" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G730" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="H730" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I730" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J730" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="731" spans="1:10" ht="28.5">
+      <c r="A731" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="B731" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C731" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D731" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E731" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="F731" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="G731" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="H731" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I731" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J731" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="732" spans="1:10" ht="28.5">
+      <c r="A732" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="B732" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C732" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D732" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E732" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="F732" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="G732" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="H732" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I732" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J732" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="733" spans="1:10" ht="28.5">
+      <c r="A733" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="B733" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C733" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D733" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E733" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="F733" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G733" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="H733" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I733" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J733" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="734" spans="1:10" ht="28.5">
+      <c r="A734" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="B734" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C734" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D734" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E734" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="F734" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G734" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="H734" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I734" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J734" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="735" spans="1:10" ht="28.5">
+      <c r="A735" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="B735" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C735" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D735" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E735" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="F735" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="G735" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="H735" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I735" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J735" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="736" spans="1:10" ht="28.5">
+      <c r="A736" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="B736" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C736" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D736" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E736" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="F736" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="G736" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="H736" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I736" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J736" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="737" spans="1:10">
+      <c r="A737" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="B737" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C737" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D737" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E737" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="F737" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="G737" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="H737" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I737" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J737" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="738" spans="1:10" ht="28.5">
+      <c r="A738" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="B738" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C738" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D738" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E738" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="F738" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="G738" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="H738" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I738" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J738" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="739" spans="1:10">
+      <c r="A739" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="B739" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C739" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D739" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E739" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F739" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="G739" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="H739" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I739" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J739" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="740" spans="1:10">
+      <c r="A740" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="B740" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C740" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D740" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E740" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F740" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="G740" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="H740" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I740" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J740" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="741" spans="1:10">
+      <c r="A741" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="B741" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C741" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D741" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E741" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="F741" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="G741" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="H741" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I741" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J741" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="742" spans="1:10" ht="28.5">
+      <c r="A742" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="B742" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C742" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D742" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E742" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="F742" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="G742" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="H742" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I742" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J742" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="743" spans="1:10" ht="28.5">
+      <c r="A743" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="B743" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C743" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D743" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E743" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F743" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G743" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="H743" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I743" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J743" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="744" spans="1:10">
+      <c r="A744" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="B744" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C744" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D744" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E744" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="F744" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="G744" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="H744" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I744" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J744" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="745" spans="1:10" ht="28.5">
+      <c r="A745" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="B745" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C745" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D745" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E745" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="F745" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="G745" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="H745" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I745" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J745" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="746" spans="1:10">
+      <c r="A746" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="B746" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C746" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D746" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E746" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="F746" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="G746" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="H746" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I746" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J746" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="747" spans="1:10">
+      <c r="A747" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="B747" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C747" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D747" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E747" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="F747" s="6" t="s">
+        <v>630</v>
+      </c>
+      <c r="G747" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="H747" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I747" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J747" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="748" spans="1:10">
+      <c r="A748" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="B748" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C748" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D748" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E748" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="F748" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="G748" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="H748" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I748" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J748" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="749" spans="1:10">
+      <c r="A749" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="B749" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C749" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D749" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E749" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F749" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="G749" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="H749" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I749" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J749" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="750" spans="1:10">
+      <c r="A750" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="B750" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C750" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D750" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E750" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="F750" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="G750" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="H750" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I750" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J750" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="751" spans="1:10" ht="28.5">
+      <c r="A751" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="B751" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C751" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D751" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E751" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="F751" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G751" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="H751" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I751" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J751" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="752" spans="1:10" ht="28.5">
+      <c r="A752" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="B752" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C752" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D752" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E752" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="F752" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="G752" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="H752" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I752" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J752" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="753" spans="1:10">
+      <c r="A753" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="B753" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C753" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D753" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E753" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="F753" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="G753" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="H753" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I753" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J753" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="754" spans="1:10" ht="28.5">
+      <c r="A754" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="B754" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C754" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D754" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E754" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="F754" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="G754" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="H754" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I754" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J754" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="755" spans="1:10">
+      <c r="A755" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="B755" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C755" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D755" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E755" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="F755" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="G755" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="H755" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I755" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J755" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="756" spans="1:10" ht="28.5">
+      <c r="A756" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="B756" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C756" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D756" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E756" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="F756" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="G756" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="H756" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I756" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J756" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="757" spans="1:10">
+      <c r="A757" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="B757" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C757" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D757" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E757" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="F757" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="G757" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="H757" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I757" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J757" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="758" spans="1:10" ht="28.5">
+      <c r="A758" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="B758" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C758" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D758" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E758" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="F758" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="G758" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="H758" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I758" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J758" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="759" spans="1:10">
+      <c r="A759" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="B759" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C759" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D759" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E759" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="F759" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="G759" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="H759" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I759" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J759" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="760" spans="1:10" ht="28.5">
+      <c r="A760" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="B760" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C760" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D760" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E760" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F760" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G760" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="H760" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I760" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J760" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="761" spans="1:10" ht="28.5">
+      <c r="A761" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="B761" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C761" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D761" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E761" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="F761" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="G761" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="H761" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I761" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J761" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="762" spans="1:10" ht="28.5">
+      <c r="A762" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="B762" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C762" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D762" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E762" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="F762" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="G762" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="H762" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I762" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J762" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="763" spans="1:10" ht="28.5">
+      <c r="A763" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="B763" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C763" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D763" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E763" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="F763" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G763" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="H763" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I763" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J763" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="764" spans="1:10" ht="28.5">
+      <c r="A764" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="B764" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C764" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D764" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E764" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="F764" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G764" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="H764" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I764" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J764" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="765" spans="1:10" ht="28.5">
+      <c r="A765" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="B765" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C765" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D765" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E765" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="F765" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="G765" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="H765" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I765" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J765" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="766" spans="1:10" ht="28.5">
+      <c r="A766" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="B766" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C766" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D766" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E766" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="F766" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="G766" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="H766" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I766" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J766" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="767" spans="1:10">
+      <c r="A767" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="B767" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C767" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D767" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E767" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="F767" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="G767" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="H767" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I767" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J767" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="768" spans="1:10" ht="28.5">
+      <c r="A768" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="B768" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C768" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D768" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E768" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="F768" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="G768" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="H768" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I768" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J768" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="769" spans="1:10">
+      <c r="A769" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="B769" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C769" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D769" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E769" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F769" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="G769" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="H769" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I769" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J769" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="770" spans="1:10">
+      <c r="A770" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="B770" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C770" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D770" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E770" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F770" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="G770" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="H770" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I770" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J770" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="771" spans="1:10">
+      <c r="A771" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="B771" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C771" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D771" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E771" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="F771" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="G771" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="H771" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I771" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J771" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="772" spans="1:10" ht="28.5">
+      <c r="A772" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="B772" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C772" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D772" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E772" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="F772" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="G772" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="H772" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I772" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J772" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="773" spans="1:10" ht="28.5">
+      <c r="A773" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="B773" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C773" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D773" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E773" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F773" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G773" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="H773" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I773" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J773" s="13" t="s">
         <v>88</v>
       </c>
     </row>
@@ -24702,26 +27191,26 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>506</v>
+        <v>546</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>507</v>
+        <v>547</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>508</v>
+        <v>548</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="B5" t="s">
-        <v>509</v>
+        <v>549</v>
       </c>
       <c r="C5" t="s">
-        <v>510</v>
+        <v>550</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -24748,66 +27237,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="28" t="s">
-        <v>511</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
+      <c r="A1" s="30" t="s">
+        <v>551</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="18" t="s">
-        <v>512</v>
+        <v>552</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>513</v>
+        <v>553</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>514</v>
+        <v>554</v>
       </c>
       <c r="B4">
-        <f>COUNTA(EVENTOS!E2:E689)</f>
-        <v>687</v>
+        <f>COUNTA(EVENTOS!E2:E773)</f>
+        <v>771</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>515</v>
+        <v>555</v>
       </c>
       <c r="B5">
-        <f>COUNTIF(EVENTOS!J2:J689,"Ejecutado")</f>
+        <f>COUNTIF(EVENTOS!J2:J773,"Ejecutado")</f>
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>516</v>
+        <v>556</v>
       </c>
       <c r="B6">
-        <f>COUNTIF(EVENTOS!J2:J689,"Pendiente")</f>
+        <f>COUNTIF(EVENTOS!J2:J773,"Pendiente")</f>
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>517</v>
+        <v>557</v>
       </c>
       <c r="B7">
-        <f>COUNTIF(EVENTOS!H2:H689,"Alta")</f>
-        <v>684</v>
+        <f>COUNTIF(EVENTOS!H2:H773,"Alta")</f>
+        <v>768</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>518</v>
+        <v>558</v>
       </c>
       <c r="B8">
-        <f>SUMPRODUCT((EVENTOS!F2:F689&lt;&gt;"")/IF(COUNTIF(EVENTOS!F2:F689,EVENTOS!F2:F689)=0,1,COUNTIF(EVENTOS!F2:F689,EVENTOS!F2:F689)))</f>
-        <v>687</v>
+        <f>SUMPRODUCT((EVENTOS!F2:F773&lt;&gt;"")/IF(COUNTIF(EVENTOS!F2:F773,EVENTOS!F2:F773)=0,1,COUNTIF(EVENTOS!F2:F773,EVENTOS!F2:F773)))</f>
+        <v>771</v>
       </c>
     </row>
   </sheetData>
@@ -24830,7 +27319,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15">
       <c r="A1" s="18" t="s">
-        <v>519</v>
+        <v>559</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -24838,111 +27327,111 @@
     </row>
     <row r="2" spans="1:4" ht="15">
       <c r="A2" s="19" t="s">
-        <v>520</v>
+        <v>560</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>521</v>
+        <v>561</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>522</v>
+        <v>562</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>523</v>
+        <v>563</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>524</v>
+        <v>564</v>
       </c>
       <c r="B3" t="s">
-        <v>525</v>
+        <v>565</v>
       </c>
       <c r="C3" t="s">
-        <v>526</v>
+        <v>566</v>
       </c>
       <c r="D3" t="s">
-        <v>527</v>
+        <v>567</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>528</v>
+        <v>568</v>
       </c>
       <c r="B4" t="s">
-        <v>529</v>
+        <v>569</v>
       </c>
       <c r="C4" t="s">
-        <v>530</v>
+        <v>570</v>
       </c>
       <c r="D4" t="s">
-        <v>531</v>
+        <v>571</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>532</v>
+        <v>572</v>
       </c>
       <c r="B5" t="s">
-        <v>533</v>
+        <v>573</v>
       </c>
       <c r="C5" t="s">
-        <v>534</v>
+        <v>574</v>
       </c>
       <c r="D5" t="s">
-        <v>535</v>
+        <v>575</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>536</v>
+        <v>576</v>
       </c>
       <c r="B6">
         <v>266</v>
       </c>
       <c r="C6" t="s">
-        <v>537</v>
+        <v>577</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>538</v>
+        <v>578</v>
       </c>
       <c r="B7" t="s">
-        <v>539</v>
+        <v>579</v>
       </c>
       <c r="C7" t="s">
-        <v>540</v>
+        <v>580</v>
       </c>
       <c r="D7" t="s">
-        <v>541</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>542</v>
+        <v>582</v>
       </c>
       <c r="B8" t="s">
-        <v>543</v>
+        <v>583</v>
       </c>
       <c r="C8" t="s">
-        <v>544</v>
+        <v>584</v>
       </c>
       <c r="D8" t="s">
-        <v>545</v>
+        <v>585</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>546</v>
+        <v>586</v>
       </c>
       <c r="B9">
         <v>403</v>
       </c>
       <c r="C9" t="s">
-        <v>547</v>
+        <v>587</v>
       </c>
       <c r="D9" t="s">
-        <v>548</v>
+        <v>588</v>
       </c>
     </row>
     <row r="10" spans="1:4">
